--- a/docs/Generated_paper/question_num_significance_test/paper/test_grammar_3_1_['No. 23_～たら〈条件(じょうけん)〉 ']_revised.xlsx
+++ b/docs/Generated_paper/question_num_significance_test/paper/test_grammar_3_1_['No. 23_～たら〈条件(じょうけん)〉 ']_revised.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -668,6 +668,1546 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>: もんだい2 雨が　ふったら　サッカーの試合は　中止　(   )　なる。</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1. に 2. で 3. を 4. が</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>: もんだい2 このボタンを　押したら、ドアが　(   )。</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1. 開きます 2. 開けます 3. 閉まります 4. 閉めます</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>: もんだい2 友だちが　来たら　いっしょ　(   )　食事を　しましょう。</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1. に 2. が 3. と 4. を</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>: もんだい2 かぜを　ひいたら、早く　寝る　(   )　いいですよ。</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>1. ほう 2. ため 3. こと 4. つもり</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>: もんだい2 お金を　ためたら、新しい　パソコン　(   )　買うつもりです。</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1. を 2. に 3. で 4. が</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>: もんだい2 駅に　着いたら　電話　(   )　ください。</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>1. して 2. し 3. した 4. します</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>: もんだい2 もし、彼に　会えたら、この　手紙を　(   )。</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1. 渡して 2. 渡す 3. 渡し 4. 渡せ</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>: もんだい2 宿題が　終わったら、遊びに　(   )　行きましょう。</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1. に 2. で 3. を 4. へ</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>: もんだい2 天気が　よかったら、明日　(   )　行きます。</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1. 海 2. 海に 3. 海で 4. 海を</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>: もんだい2 時間が　あったら、映画を　(   )　見に行きます。</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1. も 2. で 3. に 4. を</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>: もんだい3 雨が降ったら、(   )。</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1. かえります 2. かえる 3. かえりません 4. かえらない</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>: もんだい3 宿題が終わったら、(   )。</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1. あそびます 2. あそんで 3. あそばない 4. あそびません</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>: もんだい3 お金を持っていたら、(   )。</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1. 買います 2. 買いません 3. 買う 4. 買わない</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>: もんだい3 時間があったら、(   )。</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1. でかけます 2. でかけない 3. でかけません 4. でかける</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>: もんだい3 図書館に行ったら、(   )。</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1. 本を借ります 2. 本を読む 3. 本を探す 4. 本を返す</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>: もんだい3 友達が来たら、(   )。</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1. パーティーをします 2. 話をします 3. 一緒に遊びます 4. お茶を飲みます</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>: もんだい3 電車が遅れたら、(   )。</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>1. ちこくします 2. ちこくする 3. ちこくしない 4. ちこくしません</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>: もんだい3 映画が終わったら、(   )。</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1. かえります 2. ご飯を食べます 3. 散歩します 4. カフェに行きます</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>: もんだい3 もし雨が降ったら、(   )。</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1. 傘をさします 2. 雨宿りします 3. 帰ります 4. 走ります</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>: もんだい3 冬になったら、(   )。</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1. さむくなります 2. コートを着ます 3. スキーをします 4. 暖房を使います</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>: もんだい4 もし　お金が　たくさん　あったら、　新しい車を　(   ).</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1. 買いたい 2. 買うことにした 3. 買うつもり 4. 買いたがっている</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>: もんだい4 もし　雨が　降ったら、　試合は　(   ).</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1. 中止する 2. 中止したい 3. 中止するかもしれない 4. 中止した</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>: もんだい4 試験が　終わったら、　わたしは　映画を　見に行く　(   ).</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1. つもりだ 2. そうだ 3. ところだ 4. らしい</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>: もんだい4 もし　暇だったら、　手伝いに　(   ).</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>1. 行くことにする 2. 行くかもしれない 3. 行くつもり 4. 行きたがる</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>: もんだい4 もし　時間が　あったら、　新しいレストランで　食事を　(   ).</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1. することにした 2. したい 3. したがっている 4. するらしい</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>: もんだい4 仕事が　終わったら、　友だちと　カフェに　(   ).</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1. 行くことにした 2. 行きたい 3. 行くかもしれない 4. 行った</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>: もんだい4 もし　試験に　合格したら、　旅行に　(   ).</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1. 行くつもりだ 2. 行ったら 3. 行くらしい 4. 行きたい</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>: もんだい4 もし　彼が　来たら、　お祝いを　(   ).</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1. することにする 2. したがる 3. したい 4. するらしい</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>: もんだい4 もし　間違えたら、　すぐに　先生に　(   ).</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1. 聞くことにした 2. 聞きたがる 3. 聞くつもりだ 4. 聞いた</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>: もんだい4 もし　彼女が　行かないなら、　わたしも　行かない　(   ).</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1. ことにした 2. かもしれない 3. つもりだ 4. そうだ</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>: もんだい5 雨が降ったら、試合は　(   )。</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1. 中止です 2. 中止ではない 3. 中止でした 4. 中止する</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>: もんだい5 もし彼が来たら、私はすぐに　(   )。</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1. 行きます 2. 準備します 3. 話します 4. 迎えます</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>: もんだい5 この仕事が終わったら、(   )。</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1. 帰ります 2. 休みます 3. 昼ご飯を食べます 4. 散歩します</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>: もんだい5 時間があったら、映画を　(   )。</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1. 見ます 2. 読みます 3. 書きます 4. 聞きます</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>: もんだい5 彼女が手伝ったら、もっと早く　(   )。</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1. 終わります 2. 始めます 3. 続けます 4. 休みます</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>: もんだい5 この本を読んだら、次に何を　(   )。</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1. 読みますか 2. 書きますか 3. 聞きますか 4. 見ますか</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>: もんだい5 友達が来たら、ゲームを一緒に　(   )。</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1. します 2. 食べます 3. 聞きます 4. 見ます</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>: もんだい5 電車が遅れたら、授業に　(   )。</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>1. 間に合いません 2. 遅れます 3. 行きません 4. 出ません</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>: もんだい5 もしお金がたくさんあったら、旅行に　(   )。</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1. 行きたい 2. 買いたい 3. 住みたい 4. 食べたい</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>: もんだい5 彼が答えたら、みんなが　(   )。</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1. 驚きます 2. 怒ります 3. 笑います 4. 泣きます</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>: もんだい6 A:「雨が降ったら、どうしますか。 」 B:「雨が降ったら、家で映画を(   )。 」</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>1. 見ます 2. 読みます 3. 書きます 4. 食べます</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>: もんだい6 A:「もし道に迷ったら、どうしますか。 」 B:「すぐにアプリで(   )。 」</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1. 調べます 2. 見つけます 3. 探します 4. 聞きます</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>: もんだい6 A:「テストが終わったら、何をしますか。 」 B:「終わったら、友達とカフェに(   )。 」</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1. 行きます 2. 寝ます 3. 泳ぎます 4. 作ります</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>: もんだい6 A:「明日暇(ひま)だったら、何をしますか。 」 B:「暇だったら、家でゆっくり(   )。 」</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1. 休みます 2. 遊びます 3. 食べます 4. 読みます</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>: もんだい6 A:「もし、時間があったら、手伝ってもらえますか。 」 B:「時間があったら、もちろん(   )。 」</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1. 手伝います 2. 泳ぎます 3. 書きます 4. 探します</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>: もんだい6 A:「もし、今週末に予定がなかったら、どこに行きたいですか。 」 B:「予定がなかったら、海に(   )。 」</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1. 行きたいです 2. 行きます 3. 行きました 4. 行ってください</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>: もんだい6 A:「バスが遅れたら、どうしますか。 」 B:「遅れたら、タクシーを(   )。 」</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1. 使います 2. 乗ります 3. 買います 4. 売ります</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>: もんだい6 A:「もし、財布を忘れたら、どうしますか。 」 B:「忘れたら、友達に(   )。 」</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1. 借ります 2. 貸します 3. 聞きます 4. 言います</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>: もんだい6 A:「もし、雨が降ったら、ピクニックはどうしますか。 」 B:「雨が降ったら、ピクニックは(   )。 」</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1. 中止します 2. します 3. 行います 4. 開きます</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>: もんだい6 A:「試験に合格したら、何をしますか。 」 B:「合格したら、家族と(   )。 」</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1. 祝います 2. 泣きます 3. 怒ります 4. 眠ります</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>: もんだい7 もし　雨が　降ったら　(   )。</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1. 行ける 2. 行けない 3. 行こう 4. 行く</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>: もんだい7 テストが　終わったら　(   )。</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1. 映画を見に行こう 2. 映画を見ない 3. 映画が見る 4. 映画を見た</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>: もんだい7 もし　お金が　あったら、(   )。</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1. 旅行に行こう 2. 旅行に行く 3. 旅行に行かない 4. 旅行に行った</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>: もんだい7 時間が　あったら　(   )。</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>1. 勉強しない 2. 勉強しよう 3. 勉強ができる 4. 勉強することにした</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>: もんだい7 もし　彼が　来たら、(   )。</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>1. 話しなかった 2. 話そう 3. 話せる 4. 話した</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>: もんだい7 パーティーが　終わったら　(   )。</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>1. 片付ける 2. 片付けない 3. 片付けよう 4. 片付けた</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>: もんだい7 彼女が　行くと　言ったら、(   )。</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>1. 行かないことにする 2. 行くことにした 3. 行こうと思った 4. 行くことができる</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>: もんだい7 もし　道が　わからなかったら、(   )。</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>1. 聞こう 2. 聞かない 3. 聞ける 4. 聞いた</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>: もんだい7 天気が　よかったら、(   )。</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>1. ピクニックに行こう 2. ピクニックに行かない 3. ピクニックに行ける 4. ピクニックに行った</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>: もんだい7 先生が　来たら、(   )。</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>1. 授業を始めた 2. 授業を始めよう 3. 授業を始めない 4. 授業が始める</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>: もんだい8 雨が降ったら、試合は(   )中止(ちゅうし)になります。</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>1. ように 2. みたいに 3. ほどに 4. らしく</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>: もんだい8 このケーキを食べたら、まるで天国(てんごく)にいる(   )美味(おい)しさです。</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1. ような 2. らしい 3. ほど 4. みたいな</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Q3</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>: もんだい8 彼女(かのじょ)が来たら、部屋(へや)が明るくなった(   )感じ(かんじ)です。</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>1. みたいに 2. ように 3. ほどに 4. らしく</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Q4</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>: もんだい8 食事(しょくじ)が終わったら、(   )映画(えいが)を見に行きましょう。</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>1. ように 2. ほどに 3. みたいに 4. らしく</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Q5</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>: もんだい8 彼(かれ)の話(はなし)を聞いたら、夢(ゆめ)を見ている(   )気分(きぶん)になりました。</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1. らしい 2. ような 3. みたいな 4. ほど</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Q6</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>: もんだい8 お金(かね)があったら、まるで王様(おうさま)の(   )生活(せいかつ)ができるでしょう。</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1. ほど 2. ような 3. みたいな 4. らしい</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Q7</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>: もんだい8 宿題(しゅくだい)が終わったら、(   )遊(あそ)びに行けます。</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1. みたいに 2. ように 3. ほどに 4. らしく</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Q8</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>: もんだい8 彼(かれ)は試験(しけん)に合格(ごうかく)したら、(   )喜(よろこ)びました。</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1. みたいに 2. ように 3. ほどに 4. らしく</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Q9</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>: もんだい8 もし雨(あめ)が降ったら、(   )家(いえ)に帰(かえ)ります。</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>1. ほどに 2. ように 3. みたいに 4. らしく</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Q10</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>: もんだい8 彼女(かのじょ)が笑(わら)ったら、太陽(たいよう)が輝(かがや)く(   )明(あか)るいです。</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1. ように 2. みたいに 3. ほどに 4. らしく</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
